--- a/g20_results_tables/rt_sp080_10_hospitals_affiliations_frequency.xlsx
+++ b/g20_results_tables/rt_sp080_10_hospitals_affiliations_frequency.xlsx
@@ -445,7 +445,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>201</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3">
@@ -461,7 +461,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
